--- a/backend/sku_map.xlsx
+++ b/backend/sku_map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,22 +446,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10197610</t>
+          <t>5e4a9b9b-26b1-4f21-883b-43fa72837ba1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dobra Blueberry Goli Soda(PET Bottle)</t>
+          <t>Brik Oven Artisinal Sourdough Bread</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>620124</t>
+          <t>06d0fc37-fa97-430c-8d3f-07a808bb5920</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Dobra Blueberry Goli Soda</t>
+          <t>Brik Oven Artisinal Sourdough Bread</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -473,22 +473,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10161313</t>
+          <t>1ad01b68-7515-4096-a787-86b5615a30a3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dobra Bubblegum Cotton Candy(Cup)</t>
+          <t>Brik Oven Buratta Cheese</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>554766</t>
+          <t>605bfb2f-8efd-45e7-a13b-01f60b063518</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Dobra Bubblegum Cotton Candy</t>
+          <t>Brik Oven Buratta Cheese</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -500,22 +500,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10196264</t>
+          <t>a2e56f3e-88be-484f-afab-0e2de634b86d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dobra Garlic Pickle Tapioca Chips / Crisps(Pack)</t>
+          <t>Brik Oven Honey &amp; Oats Sourdough Bread</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>618144</t>
+          <t>243eb96d-1284-49d7-aa72-1f874a4fc33f</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dobra Garlic Pickle Tapioca Chips / Crisps</t>
+          <t>Brik Oven Honey &amp; Oats Sourdough Bread</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -527,22 +527,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10197566</t>
+          <t>72447115-ccb1-463b-89cc-fa8b84323e5d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dobra Mango Goli Soda(PET Bottle)</t>
+          <t>Brik Oven Pizza Mozzeralla Cheese</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>620055</t>
+          <t>9c16759b-7fb1-46eb-8651-90f433782d86</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dobra Mango Goli Soda</t>
+          <t>Brik Oven Pizza Mozzeralla Cheese</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -554,22 +554,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10196263</t>
+          <t>4770571e-2278-4efa-a152-9e5664eaae0b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dobra Plain Salted Tapioca Chips / Crisps(Pack)</t>
+          <t>Brik Oven Pretzel Bagel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>618143</t>
+          <t>42f244fb-a591-4c43-9e14-406444c847ef</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Dobra Plain Salted Tapioca Chips / Crisps</t>
+          <t>Brik Oven Pretzel Bagel</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -581,22 +581,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10161333</t>
+          <t>36d20079-6294-4af9-b027-c7870b6c763b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dobra Pop Goli Soda - Apple Mojito(PET Bottle)</t>
+          <t>Brik Oven Rosemary &amp; Cheddar Cheese Sour Dough Bread</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>554786</t>
+          <t>78297c5c-5755-46f6-b4b4-b45675fb931c</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dobra Pop Goli Soda - Apple Mojito</t>
+          <t>Brik Oven Rosemary &amp; Cheddar Cheese Sour Dough Bread</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -608,22 +608,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10196278</t>
+          <t>af62829a-99d3-4049-8614-401f9523f79d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dobra Pop Goli Soda - Grape(PET Bottle)</t>
+          <t>Brik Oven Sour Cream</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>618158</t>
+          <t>0d05de1d-321f-4f21-a1a2-fbd10ee0a575</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dobra Pop Goli Soda - Grape</t>
+          <t>Brik Oven Sour Cream</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -635,22 +635,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10161332</t>
+          <t>4ea969c6-c13b-4243-9871-ff5dbdb369d3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dobra Pop Goli Soda - Kokum Jeera(PET Bottle)</t>
+          <t>Brik Oven Whey Ricotta Cheese</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>554785</t>
+          <t>d7ca2e33-0f01-4a76-8a1c-215517a1a00b</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dobra Pop Goli Soda - Kokum Jeera</t>
+          <t>Brik Oven Whey Ricotta Cheese</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -662,160 +662,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10161331</t>
+          <t>49665e03-a09c-4a51-b5e0-cda18d152544</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dobra Pop Goli Soda - Nimbu Masala(PET Bottle)</t>
+          <t>Brik Oven Whole Wheat Sourdough Bread</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>554784</t>
+          <t>0e8e3c72-a70e-44c5-8987-1f16520b41ed</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dobra Pop Goli Soda - Nimbu Masala</t>
+          <t>Brik Oven Whole Wheat Sourdough Bread</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10246891</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Dobra Rose Apple Soda(PET Bottle)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>693070</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Dobra Rose Apple Soda</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10196266</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dobra Smoky Barbeque Tapioca Chips / Crisps(Pack)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>618146</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Dobra Smoky Barbeque Tapioca Chips / Crisps</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>10161330</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Dobra Spicy Kari Tapioca Chips /Crisps(Packet)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>554783</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Dobra Spicy Kari Tapioca Chips /Crisps</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>10161314</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Dobra Strawberry Blast Cotton Candy(Cup)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>554767</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Dobra Strawberry Blast Cotton Candy</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>10161326</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Dobra Tangy Tomato Tapioca Chips /Crisps(Packet)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>554779</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Dobra Tangy Tomato Tapioca Chips /Crisps</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
